--- a/outputs/2. City of York Council (Final).xlsx
+++ b/outputs/2. City of York Council (Final).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,7 +466,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Risk Index</t>
+          <t>Risk Priority (low, med, high)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -476,12 +476,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Impact Description</t>
+          <t>Mitigating Action</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Mitigating Action</t>
+          <t>Result</t>
         </is>
       </c>
     </row>
@@ -511,8 +511,10 @@
       <c r="G2" t="n">
         <v>1.6666666667</v>
       </c>
-      <c r="H2" t="n">
-        <v>2</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -552,8 +554,10 @@
       <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="H3" t="n">
-        <v>14</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -597,8 +601,10 @@
       <c r="G4" t="n">
         <v>3.3333333333</v>
       </c>
-      <c r="H4" t="n">
-        <v>4</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -642,8 +648,10 @@
       <c r="G5" t="n">
         <v>3.3333333333</v>
       </c>
-      <c r="H5" t="n">
-        <v>4</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -687,8 +695,10 @@
       <c r="G6" t="n">
         <v>1.6666666667</v>
       </c>
-      <c r="H6" t="n">
-        <v>2</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -732,8 +742,10 @@
       <c r="G7" t="n">
         <v>6.6666666667</v>
       </c>
-      <c r="H7" t="n">
-        <v>10.5</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -777,8 +789,10 @@
       <c r="G8" t="n">
         <v>8.333333333300001</v>
       </c>
-      <c r="H8" t="n">
-        <v>15</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -822,8 +836,10 @@
       <c r="G9" t="n">
         <v>5</v>
       </c>
-      <c r="H9" t="n">
-        <v>9</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -867,8 +883,10 @@
       <c r="G10" t="n">
         <v>5</v>
       </c>
-      <c r="H10" t="n">
-        <v>12</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -912,8 +930,10 @@
       <c r="G11" t="n">
         <v>8.333333333300001</v>
       </c>
-      <c r="H11" t="n">
-        <v>3</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -957,8 +977,10 @@
       <c r="G12" t="n">
         <v>8.333333333300001</v>
       </c>
-      <c r="H12" t="n">
-        <v>5</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1002,8 +1024,10 @@
       <c r="G13" t="n">
         <v>3.3333333333</v>
       </c>
-      <c r="H13" t="n">
-        <v>4</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1047,8 +1071,10 @@
       <c r="G14" t="n">
         <v>1.6666666667</v>
       </c>
-      <c r="H14" t="n">
-        <v>1</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1092,8 +1118,10 @@
       <c r="G15" t="n">
         <v>5</v>
       </c>
-      <c r="H15" t="n">
-        <v>2.5</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1137,8 +1165,10 @@
       <c r="G16" t="n">
         <v>8.333333333300001</v>
       </c>
-      <c r="H16" t="n">
-        <v>24</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1182,8 +1212,10 @@
       <c r="G17" t="n">
         <v>5</v>
       </c>
-      <c r="H17" t="n">
-        <v>9</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1227,8 +1259,10 @@
       <c r="G18" t="n">
         <v>8.333333333300001</v>
       </c>
-      <c r="H18" t="n">
-        <v>15</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,9 +1306,7 @@
       <c r="G19" t="n">
         <v>6.6666666667</v>
       </c>
-      <c r="H19" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Structural Engineer</t>
@@ -1317,8 +1349,10 @@
       <c r="G20" t="n">
         <v>5</v>
       </c>
-      <c r="H20" t="n">
-        <v>6</v>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1362,8 +1396,10 @@
       <c r="G21" t="n">
         <v>6.6666666667</v>
       </c>
-      <c r="H21" t="n">
-        <v>4.5</v>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1407,8 +1443,10 @@
       <c r="G22" t="n">
         <v>5</v>
       </c>
-      <c r="H22" t="n">
-        <v>12</v>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1452,8 +1490,10 @@
       <c r="G23" t="n">
         <v>6.6666666667</v>
       </c>
-      <c r="H23" t="n">
-        <v>14</v>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1497,8 +1537,10 @@
       <c r="G24" t="n">
         <v>5</v>
       </c>
-      <c r="H24" t="n">
-        <v>4</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1542,8 +1584,10 @@
       <c r="G25" t="n">
         <v>5</v>
       </c>
-      <c r="H25" t="n">
-        <v>15</v>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1587,8 +1631,10 @@
       <c r="G26" t="n">
         <v>5</v>
       </c>
-      <c r="H26" t="n">
-        <v>9</v>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1632,8 +1678,10 @@
       <c r="G27" t="n">
         <v>5</v>
       </c>
-      <c r="H27" t="n">
-        <v>9</v>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1677,8 +1725,10 @@
       <c r="G28" t="n">
         <v>5</v>
       </c>
-      <c r="H28" t="n">
-        <v>6</v>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1722,8 +1772,10 @@
       <c r="G29" t="n">
         <v>6.6666666667</v>
       </c>
-      <c r="H29" t="n">
-        <v>2.5</v>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1767,8 +1819,10 @@
       <c r="G30" t="n">
         <v>8.333333333300001</v>
       </c>
-      <c r="H30" t="n">
-        <v>9</v>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1812,8 +1866,10 @@
       <c r="G31" t="n">
         <v>5</v>
       </c>
-      <c r="H31" t="n">
-        <v>12</v>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1853,8 +1909,10 @@
       <c r="G32" t="n">
         <v>1.6666666667</v>
       </c>
-      <c r="H32" t="n">
-        <v>6</v>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1898,8 +1956,10 @@
       <c r="G33" t="n">
         <v>8.333333333300001</v>
       </c>
-      <c r="H33" t="n">
-        <v>4.5</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1943,8 +2003,10 @@
       <c r="G34" t="n">
         <v>5</v>
       </c>
-      <c r="H34" t="n">
-        <v>9</v>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1988,8 +2050,10 @@
       <c r="G35" t="n">
         <v>8.333333333300001</v>
       </c>
-      <c r="H35" t="n">
-        <v>30</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2003,7 +2067,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Traditional contract — risk with CYC; secure adequate contingency</t>
+          <t>Traditional contract - risk with CYC; secure adequate contingency</t>
         </is>
       </c>
     </row>
@@ -2033,8 +2097,10 @@
       <c r="G36" t="n">
         <v>5</v>
       </c>
-      <c r="H36" t="n">
-        <v>12.5</v>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2078,8 +2144,10 @@
       <c r="G37" t="n">
         <v>8.333333333300001</v>
       </c>
-      <c r="H37" t="n">
-        <v>10</v>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2123,8 +2191,10 @@
       <c r="G38" t="n">
         <v>5</v>
       </c>
-      <c r="H38" t="n">
-        <v>9</v>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2138,7 +2208,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Additional bore hole surveys indertaken, no foundatons / obstructions found albeit at relatively shallow depth. (near tower) Bullivants / Arup to review surveys and confirm they are happy with findings. Vinci to design piling to new structures and confirm site information held is adequate</t>
+          <t>Additional bore hole surveys undertaken, no foundations / obstructions found albeit at relatively shallow depth. (near tower) Bullivants / Arup to review surveys and confirm they are happy with findings. Vinci to design piling to new structures and confirm site information held is adequate</t>
         </is>
       </c>
     </row>
@@ -2168,8 +2238,10 @@
       <c r="G39" t="n">
         <v>3.3333333333</v>
       </c>
-      <c r="H39" t="n">
-        <v>6</v>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2213,8 +2285,10 @@
       <c r="G40" t="n">
         <v>3.3333333333</v>
       </c>
-      <c r="H40" t="n">
-        <v>7.5</v>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2258,8 +2332,10 @@
       <c r="G41" t="n">
         <v>5</v>
       </c>
-      <c r="H41" t="n">
-        <v>3</v>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2273,7 +2349,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Trial hole dug in the location and appears to be clear - risk to be reviewed again once demoliton of north annex is complete.</t>
+          <t>Trial hole dug in the location and appears to be clear - risk to be reviewed again once demolition of north annex is complete.</t>
         </is>
       </c>
     </row>
@@ -2303,8 +2379,10 @@
       <c r="G42" t="n">
         <v>8.333333333300001</v>
       </c>
-      <c r="H42" t="n">
-        <v>18</v>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2348,8 +2426,10 @@
       <c r="G43" t="n">
         <v>8.333333333300001</v>
       </c>
-      <c r="H43" t="n">
-        <v>27</v>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2393,8 +2473,10 @@
       <c r="G44" t="n">
         <v>6.6666666667</v>
       </c>
-      <c r="H44" t="n">
-        <v>8</v>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2438,8 +2520,10 @@
       <c r="G45" t="n">
         <v>3.3333333333</v>
       </c>
-      <c r="H45" t="n">
-        <v>5</v>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2483,8 +2567,10 @@
       <c r="G46" t="n">
         <v>5</v>
       </c>
-      <c r="H46" t="n">
-        <v>6</v>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
